--- a/output/Jiangxi/宜春市_news.xlsx
+++ b/output/Jiangxi/宜春市_news.xlsx
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="M2" t="n">
         <v>18</v>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M4" t="n">
         <v>6</v>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>84239</v>
+        <v>91112</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2023-12-25</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1601,7 +1601,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="M17" t="n">
         <v>4</v>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="M19" t="n">
         <v>25</v>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M20" t="n">
         <v>1</v>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2119,7 +2119,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2193,7 +2193,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="M27" t="n">
         <v>22</v>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M28" t="n">
         <v>3</v>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2624,7 +2624,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>5070</v>
+        <v>5106</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="M34" t="n">
         <v>29</v>
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M40" t="n">
         <v>3</v>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3438,7 +3438,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -3969,7 +3969,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -4339,7 +4339,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M53" t="n">
         <v>5</v>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -4635,7 +4635,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M59" t="n">
         <v>4</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
@@ -5227,7 +5227,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="M65" t="n">
         <v>1</v>
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -5375,7 +5375,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -5597,7 +5597,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -5745,7 +5745,7 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -5893,7 +5893,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -5967,7 +5967,7 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -6115,7 +6115,7 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -6263,7 +6263,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M79" t="n">
         <v>2</v>
@@ -6337,7 +6337,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -6411,7 +6411,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
@@ -6707,7 +6707,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -6781,7 +6781,7 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -6855,7 +6855,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -6929,7 +6929,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -7003,7 +7003,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="M89" t="n">
         <v>2</v>
@@ -7077,7 +7077,7 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -7151,7 +7151,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M91" t="n">
         <v>0</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
@@ -7373,7 +7373,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M95" t="n">
         <v>5</v>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M96" t="n">
         <v>0</v>
@@ -7595,7 +7595,7 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
@@ -7669,7 +7669,7 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M98" t="n">
         <v>1</v>
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
@@ -7817,7 +7817,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
@@ -7965,7 +7965,7 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="M102" t="n">
         <v>0</v>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2022-10-28</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="M104" t="n">
         <v>0</v>
@@ -8187,7 +8187,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M105" t="n">
         <v>0</v>
@@ -8261,7 +8261,7 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M106" t="n">
         <v>0</v>
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="M107" t="n">
         <v>0</v>
@@ -8409,7 +8409,7 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M108" t="n">
         <v>0</v>
@@ -8483,7 +8483,7 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M109" t="n">
         <v>0</v>
@@ -8557,7 +8557,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M110" t="n">
         <v>2</v>
@@ -8631,7 +8631,7 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M111" t="n">
         <v>0</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M112" t="n">
         <v>0</v>
@@ -8779,7 +8779,7 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="M113" t="n">
         <v>0</v>
@@ -8853,7 +8853,7 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M114" t="n">
         <v>0</v>
@@ -8927,7 +8927,7 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="M115" t="n">
         <v>0</v>
@@ -9001,7 +9001,7 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M116" t="n">
         <v>0</v>
@@ -9075,7 +9075,7 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M117" t="n">
         <v>0</v>
@@ -9149,7 +9149,7 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="M118" t="n">
         <v>0</v>
@@ -9223,7 +9223,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M119" t="n">
         <v>0</v>
@@ -9297,7 +9297,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M120" t="n">
         <v>0</v>
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M121" t="n">
         <v>3</v>
@@ -9445,7 +9445,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M122" t="n">
         <v>9</v>
@@ -9519,7 +9519,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M123" t="n">
         <v>2</v>
@@ -9593,7 +9593,7 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M124" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M125" t="n">
         <v>0</v>
@@ -9741,7 +9741,7 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="M126" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M127" t="n">
         <v>0</v>
@@ -9889,7 +9889,7 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M128" t="n">
         <v>0</v>
@@ -9941,7 +9941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -9950,7 +9950,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>7189</v>
+        <v>7225</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M129" t="n">
         <v>0</v>
@@ -10037,7 +10037,7 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M130" t="n">
         <v>0</v>
@@ -10111,7 +10111,7 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M131" t="n">
         <v>1</v>
@@ -10185,7 +10185,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M132" t="n">
         <v>0</v>
@@ -10259,7 +10259,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M133" t="n">
         <v>0</v>
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="M134" t="n">
         <v>2</v>
@@ -10407,7 +10407,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M135" t="n">
         <v>0</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="M136" t="n">
         <v>24</v>
@@ -10555,7 +10555,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="M137" t="n">
         <v>2</v>
@@ -10629,7 +10629,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M138" t="n">
         <v>0</v>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2022-10-28</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M139" t="n">
         <v>0</v>
@@ -10777,7 +10777,7 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M140" t="n">
         <v>0</v>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M141" t="n">
         <v>0</v>
@@ -10925,7 +10925,7 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M142" t="n">
         <v>0</v>
@@ -10999,7 +10999,7 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M143" t="n">
         <v>0</v>
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M144" t="n">
         <v>0</v>
@@ -11147,7 +11147,7 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M145" t="n">
         <v>3</v>
@@ -11221,7 +11221,7 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M146" t="n">
         <v>0</v>
@@ -11295,7 +11295,7 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="M147" t="n">
         <v>0</v>
@@ -11369,7 +11369,7 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M148" t="n">
         <v>0</v>
@@ -11443,7 +11443,7 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M149" t="n">
         <v>0</v>
@@ -11517,7 +11517,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M150" t="n">
         <v>0</v>
@@ -11591,7 +11591,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M151" t="n">
         <v>0</v>
@@ -11665,7 +11665,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M152" t="n">
         <v>0</v>
@@ -11739,7 +11739,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="M153" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M154" t="n">
         <v>3</v>
@@ -11887,7 +11887,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M155" t="n">
         <v>0</v>
@@ -11961,7 +11961,7 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M156" t="n">
         <v>0</v>
@@ -12035,7 +12035,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M157" t="n">
         <v>1</v>
@@ -12109,7 +12109,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M158" t="n">
         <v>0</v>
@@ -12183,7 +12183,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M159" t="n">
         <v>0</v>
@@ -12257,7 +12257,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M160" t="n">
         <v>0</v>
@@ -12331,7 +12331,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M161" t="n">
         <v>0</v>
@@ -12405,7 +12405,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M162" t="n">
         <v>0</v>
@@ -12457,7 +12457,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2022-10-28</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -12479,7 +12479,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M163" t="n">
         <v>2</v>
@@ -12553,7 +12553,7 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M164" t="n">
         <v>0</v>
@@ -12627,7 +12627,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M165" t="n">
         <v>0</v>
@@ -12701,7 +12701,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M166" t="n">
         <v>0</v>
@@ -12775,7 +12775,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M167" t="n">
         <v>0</v>
@@ -12849,7 +12849,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M168" t="n">
         <v>0</v>
@@ -12923,7 +12923,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="M169" t="n">
         <v>0</v>
@@ -12997,7 +12997,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M170" t="n">
         <v>0</v>
@@ -13071,7 +13071,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M171" t="n">
         <v>0</v>
@@ -13145,7 +13145,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M172" t="n">
         <v>7</v>
@@ -13219,7 +13219,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M173" t="n">
         <v>7</v>
@@ -13293,7 +13293,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="M174" t="n">
         <v>0</v>
@@ -13367,7 +13367,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M175" t="n">
         <v>0</v>
@@ -13441,7 +13441,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M176" t="n">
         <v>0</v>
@@ -13515,7 +13515,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M177" t="n">
         <v>0</v>
@@ -13589,7 +13589,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M178" t="n">
         <v>0</v>
@@ -13663,7 +13663,7 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="M179" t="n">
         <v>0</v>
@@ -13737,7 +13737,7 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M180" t="n">
         <v>0</v>
@@ -13811,7 +13811,7 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M181" t="n">
         <v>0</v>
@@ -13885,7 +13885,7 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M182" t="n">
         <v>0</v>
@@ -13959,7 +13959,7 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M183" t="n">
         <v>0</v>
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M184" t="n">
         <v>0</v>
@@ -14107,7 +14107,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M185" t="n">
         <v>0</v>
@@ -14181,7 +14181,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M186" t="n">
         <v>0</v>
@@ -14255,7 +14255,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M187" t="n">
         <v>0</v>
@@ -14329,7 +14329,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M188" t="n">
         <v>0</v>
@@ -14403,7 +14403,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M189" t="n">
         <v>0</v>
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M190" t="n">
         <v>0</v>
@@ -14551,7 +14551,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M191" t="n">
         <v>2</v>
@@ -14625,7 +14625,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M192" t="n">
         <v>0</v>
@@ -14699,7 +14699,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M193" t="n">
         <v>0</v>
@@ -14773,7 +14773,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="M194" t="n">
         <v>1</v>
@@ -14847,7 +14847,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M195" t="n">
         <v>0</v>
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M196" t="n">
         <v>0</v>
@@ -14995,7 +14995,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M197" t="n">
         <v>0</v>
@@ -15069,7 +15069,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M198" t="n">
         <v>2</v>
@@ -15143,7 +15143,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M199" t="n">
         <v>3</v>
@@ -15217,7 +15217,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="M200" t="n">
         <v>0</v>
@@ -15291,7 +15291,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M201" t="n">
         <v>4</v>
@@ -15365,7 +15365,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M202" t="n">
         <v>0</v>
@@ -15439,7 +15439,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M203" t="n">
         <v>12</v>
@@ -15513,7 +15513,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M204" t="n">
         <v>0</v>
@@ -15587,7 +15587,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M205" t="n">
         <v>0</v>
@@ -15661,7 +15661,7 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M206" t="n">
         <v>0</v>
@@ -15735,7 +15735,7 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M207" t="n">
         <v>0</v>
@@ -15809,7 +15809,7 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M208" t="n">
         <v>0</v>
@@ -15883,7 +15883,7 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M209" t="n">
         <v>0</v>
@@ -15957,7 +15957,7 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M210" t="n">
         <v>0</v>
@@ -16031,7 +16031,7 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="M211" t="n">
         <v>0</v>
@@ -16105,7 +16105,7 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M212" t="n">
         <v>0</v>
@@ -16179,7 +16179,7 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M213" t="n">
         <v>0</v>
@@ -16253,7 +16253,7 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M214" t="n">
         <v>0</v>
@@ -16327,7 +16327,7 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M215" t="n">
         <v>0</v>
@@ -16401,7 +16401,7 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M216" t="n">
         <v>0</v>
@@ -16475,7 +16475,7 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M217" t="n">
         <v>0</v>
@@ -16527,7 +16527,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -16536,7 +16536,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M218" t="n">
         <v>0</v>
@@ -16623,7 +16623,7 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M219" t="n">
         <v>0</v>
@@ -16697,7 +16697,7 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M220" t="n">
         <v>0</v>
@@ -16771,7 +16771,7 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M221" t="n">
         <v>0</v>
@@ -16845,7 +16845,7 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M222" t="n">
         <v>0</v>
@@ -16919,7 +16919,7 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M223" t="n">
         <v>1</v>
@@ -16993,7 +16993,7 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M224" t="n">
         <v>0</v>
@@ -17067,7 +17067,7 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="M225" t="n">
         <v>0</v>
@@ -17141,7 +17141,7 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M226" t="n">
         <v>1</v>
@@ -17215,7 +17215,7 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M227" t="n">
         <v>0</v>
@@ -17289,7 +17289,7 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M228" t="n">
         <v>0</v>
@@ -17363,7 +17363,7 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M229" t="n">
         <v>0</v>
@@ -17415,7 +17415,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -17424,7 +17424,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J230" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M230" t="n">
         <v>0</v>
@@ -17511,7 +17511,7 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M231" t="n">
         <v>0</v>
@@ -17585,7 +17585,7 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M232" t="n">
         <v>0</v>
@@ -17659,7 +17659,7 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M233" t="n">
         <v>0</v>
@@ -17733,7 +17733,7 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M234" t="n">
         <v>0</v>
@@ -17807,7 +17807,7 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M235" t="n">
         <v>0</v>
@@ -17881,7 +17881,7 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M236" t="n">
         <v>0</v>
@@ -17955,7 +17955,7 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M237" t="n">
         <v>7</v>
@@ -18029,7 +18029,7 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M238" t="n">
         <v>0</v>
@@ -18103,7 +18103,7 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M239" t="n">
         <v>0</v>
@@ -18155,7 +18155,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2022-10-28</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -18177,7 +18177,7 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M240" t="n">
         <v>0</v>
@@ -18251,7 +18251,7 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M241" t="n">
         <v>0</v>
@@ -18325,7 +18325,7 @@
         </is>
       </c>
       <c r="L242" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M242" t="n">
         <v>0</v>
@@ -18399,7 +18399,7 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M243" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M244" t="n">
         <v>0</v>
@@ -18547,7 +18547,7 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M245" t="n">
         <v>0</v>
@@ -18599,7 +18599,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -18621,7 +18621,7 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M246" t="n">
         <v>0</v>
@@ -18695,7 +18695,7 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M247" t="n">
         <v>0</v>
@@ -18769,7 +18769,7 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M248" t="n">
         <v>0</v>
@@ -18843,7 +18843,7 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M249" t="n">
         <v>0</v>
@@ -18917,7 +18917,7 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M250" t="n">
         <v>0</v>
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M251" t="n">
         <v>1</v>
@@ -19065,7 +19065,7 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M252" t="n">
         <v>0</v>
@@ -19139,7 +19139,7 @@
         </is>
       </c>
       <c r="L253" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M253" t="n">
         <v>0</v>
@@ -19213,7 +19213,7 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M254" t="n">
         <v>0</v>
@@ -19287,7 +19287,7 @@
         </is>
       </c>
       <c r="L255" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M255" t="n">
         <v>0</v>
@@ -19361,7 +19361,7 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M256" t="n">
         <v>0</v>
@@ -19435,7 +19435,7 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M257" t="n">
         <v>0</v>
@@ -19509,7 +19509,7 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M258" t="n">
         <v>0</v>
@@ -19583,7 +19583,7 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M259" t="n">
         <v>0</v>
@@ -19657,7 +19657,7 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M260" t="n">
         <v>1</v>
@@ -19731,7 +19731,7 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M261" t="n">
         <v>4</v>
@@ -19805,7 +19805,7 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M262" t="n">
         <v>0</v>
@@ -19879,7 +19879,7 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M263" t="n">
         <v>0</v>
@@ -19953,7 +19953,7 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M264" t="n">
         <v>2</v>
@@ -20027,7 +20027,7 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M265" t="n">
         <v>0</v>
@@ -20101,7 +20101,7 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M266" t="n">
         <v>0</v>
@@ -20175,7 +20175,7 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M267" t="n">
         <v>0</v>
@@ -20249,7 +20249,7 @@
         </is>
       </c>
       <c r="L268" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M268" t="n">
         <v>0</v>
@@ -20323,7 +20323,7 @@
         </is>
       </c>
       <c r="L269" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M269" t="n">
         <v>0</v>
@@ -20397,7 +20397,7 @@
         </is>
       </c>
       <c r="L270" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M270" t="n">
         <v>0</v>
@@ -20471,7 +20471,7 @@
         </is>
       </c>
       <c r="L271" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M271" t="n">
         <v>1</v>
@@ -20545,7 +20545,7 @@
         </is>
       </c>
       <c r="L272" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M272" t="n">
         <v>0</v>
@@ -20619,7 +20619,7 @@
         </is>
       </c>
       <c r="L273" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M273" t="n">
         <v>0</v>
@@ -20693,7 +20693,7 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M274" t="n">
         <v>3</v>
@@ -20767,7 +20767,7 @@
         </is>
       </c>
       <c r="L275" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M275" t="n">
         <v>0</v>
@@ -20841,7 +20841,7 @@
         </is>
       </c>
       <c r="L276" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M276" t="n">
         <v>0</v>
@@ -20915,7 +20915,7 @@
         </is>
       </c>
       <c r="L277" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M277" t="n">
         <v>0</v>
@@ -20989,7 +20989,7 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M278" t="n">
         <v>0</v>
@@ -21063,7 +21063,7 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M279" t="n">
         <v>0</v>
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="I280" t="n">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="J280" t="inlineStr">
         <is>
@@ -21137,7 +21137,7 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M280" t="n">
         <v>0</v>
@@ -21211,7 +21211,7 @@
         </is>
       </c>
       <c r="L281" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M281" t="n">
         <v>0</v>
@@ -21285,7 +21285,7 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M282" t="n">
         <v>0</v>
@@ -21359,7 +21359,7 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M283" t="n">
         <v>0</v>
@@ -21433,7 +21433,7 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M284" t="n">
         <v>0</v>
@@ -21507,7 +21507,7 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M285" t="n">
         <v>0</v>
@@ -21581,7 +21581,7 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="M286" t="n">
         <v>11</v>
@@ -21655,7 +21655,7 @@
         </is>
       </c>
       <c r="L287" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M287" t="n">
         <v>0</v>
@@ -21729,7 +21729,7 @@
         </is>
       </c>
       <c r="L288" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M288" t="n">
         <v>0</v>
@@ -21803,7 +21803,7 @@
         </is>
       </c>
       <c r="L289" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M289" t="n">
         <v>19</v>
@@ -21877,7 +21877,7 @@
         </is>
       </c>
       <c r="L290" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M290" t="n">
         <v>0</v>
@@ -21951,7 +21951,7 @@
         </is>
       </c>
       <c r="L291" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M291" t="n">
         <v>0</v>
@@ -22025,7 +22025,7 @@
         </is>
       </c>
       <c r="L292" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M292" t="n">
         <v>0</v>
@@ -22099,7 +22099,7 @@
         </is>
       </c>
       <c r="L293" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M293" t="n">
         <v>0</v>
@@ -22173,7 +22173,7 @@
         </is>
       </c>
       <c r="L294" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M294" t="n">
         <v>2</v>
@@ -22247,7 +22247,7 @@
         </is>
       </c>
       <c r="L295" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M295" t="n">
         <v>2</v>
@@ -22321,7 +22321,7 @@
         </is>
       </c>
       <c r="L296" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M296" t="n">
         <v>0</v>
@@ -22395,7 +22395,7 @@
         </is>
       </c>
       <c r="L297" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M297" t="n">
         <v>0</v>
@@ -22469,7 +22469,7 @@
         </is>
       </c>
       <c r="L298" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M298" t="n">
         <v>1</v>
@@ -22543,7 +22543,7 @@
         </is>
       </c>
       <c r="L299" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M299" t="n">
         <v>2</v>
@@ -22617,7 +22617,7 @@
         </is>
       </c>
       <c r="L300" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M300" t="n">
         <v>0</v>
@@ -22691,7 +22691,7 @@
         </is>
       </c>
       <c r="L301" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M301" t="n">
         <v>0</v>
@@ -22765,7 +22765,7 @@
         </is>
       </c>
       <c r="L302" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M302" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>2023-12-25</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -22826,7 +22826,7 @@
         </is>
       </c>
       <c r="I303" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J303" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         </is>
       </c>
       <c r="L303" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M303" t="n">
         <v>0</v>
@@ -22913,7 +22913,7 @@
         </is>
       </c>
       <c r="L304" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M304" t="n">
         <v>0</v>
@@ -22987,7 +22987,7 @@
         </is>
       </c>
       <c r="L305" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M305" t="n">
         <v>0</v>
@@ -23061,7 +23061,7 @@
         </is>
       </c>
       <c r="L306" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M306" t="n">
         <v>0</v>
@@ -23135,7 +23135,7 @@
         </is>
       </c>
       <c r="L307" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M307" t="n">
         <v>0</v>
@@ -23209,7 +23209,7 @@
         </is>
       </c>
       <c r="L308" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M308" t="n">
         <v>0</v>
@@ -23283,7 +23283,7 @@
         </is>
       </c>
       <c r="L309" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M309" t="n">
         <v>0</v>
@@ -23357,7 +23357,7 @@
         </is>
       </c>
       <c r="L310" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M310" t="n">
         <v>0</v>
@@ -23431,7 +23431,7 @@
         </is>
       </c>
       <c r="L311" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M311" t="n">
         <v>2</v>
@@ -23505,7 +23505,7 @@
         </is>
       </c>
       <c r="L312" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M312" t="n">
         <v>0</v>
@@ -23579,7 +23579,7 @@
         </is>
       </c>
       <c r="L313" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M313" t="n">
         <v>0</v>
@@ -23653,7 +23653,7 @@
         </is>
       </c>
       <c r="L314" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M314" t="n">
         <v>0</v>
@@ -23727,7 +23727,7 @@
         </is>
       </c>
       <c r="L315" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M315" t="n">
         <v>0</v>
@@ -23801,7 +23801,7 @@
         </is>
       </c>
       <c r="L316" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M316" t="n">
         <v>0</v>
@@ -23875,7 +23875,7 @@
         </is>
       </c>
       <c r="L317" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M317" t="n">
         <v>0</v>
@@ -23949,7 +23949,7 @@
         </is>
       </c>
       <c r="L318" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M318" t="n">
         <v>0</v>
@@ -24001,7 +24001,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>2023-11-10</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -24010,7 +24010,7 @@
         </is>
       </c>
       <c r="I319" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J319" t="inlineStr">
         <is>
@@ -24023,7 +24023,7 @@
         </is>
       </c>
       <c r="L319" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M319" t="n">
         <v>0</v>
@@ -24097,7 +24097,7 @@
         </is>
       </c>
       <c r="L320" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M320" t="n">
         <v>0</v>
@@ -24171,7 +24171,7 @@
         </is>
       </c>
       <c r="L321" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M321" t="n">
         <v>0</v>
@@ -24245,7 +24245,7 @@
         </is>
       </c>
       <c r="L322" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M322" t="n">
         <v>0</v>
@@ -24319,7 +24319,7 @@
         </is>
       </c>
       <c r="L323" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M323" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
         </is>
       </c>
       <c r="L324" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M324" t="n">
         <v>0</v>
@@ -24467,7 +24467,7 @@
         </is>
       </c>
       <c r="L325" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="M325" t="n">
         <v>1</v>
@@ -24541,7 +24541,7 @@
         </is>
       </c>
       <c r="L326" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="M326" t="n">
         <v>0</v>
@@ -24615,7 +24615,7 @@
         </is>
       </c>
       <c r="L327" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M327" t="n">
         <v>0</v>
@@ -24689,7 +24689,7 @@
         </is>
       </c>
       <c r="L328" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M328" t="n">
         <v>0</v>
@@ -24763,7 +24763,7 @@
         </is>
       </c>
       <c r="L329" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M329" t="n">
         <v>0</v>
@@ -24837,7 +24837,7 @@
         </is>
       </c>
       <c r="L330" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M330" t="n">
         <v>0</v>
@@ -24911,7 +24911,7 @@
         </is>
       </c>
       <c r="L331" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M331" t="n">
         <v>2</v>
@@ -24985,7 +24985,7 @@
         </is>
       </c>
       <c r="L332" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="M332" t="n">
         <v>0</v>
@@ -25059,7 +25059,7 @@
         </is>
       </c>
       <c r="L333" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="M333" t="n">
         <v>0</v>
@@ -25133,7 +25133,7 @@
         </is>
       </c>
       <c r="L334" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M334" t="n">
         <v>0</v>
@@ -25207,7 +25207,7 @@
         </is>
       </c>
       <c r="L335" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M335" t="n">
         <v>0</v>
@@ -25281,7 +25281,7 @@
         </is>
       </c>
       <c r="L336" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M336" t="n">
         <v>0</v>
@@ -25355,7 +25355,7 @@
         </is>
       </c>
       <c r="L337" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M337" t="n">
         <v>0</v>
@@ -25429,7 +25429,7 @@
         </is>
       </c>
       <c r="L338" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M338" t="n">
         <v>0</v>
@@ -25503,7 +25503,7 @@
         </is>
       </c>
       <c r="L339" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M339" t="n">
         <v>0</v>
@@ -25577,7 +25577,7 @@
         </is>
       </c>
       <c r="L340" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M340" t="n">
         <v>0</v>
@@ -25651,7 +25651,7 @@
         </is>
       </c>
       <c r="L341" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M341" t="n">
         <v>0</v>
@@ -25725,7 +25725,7 @@
         </is>
       </c>
       <c r="L342" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M342" t="n">
         <v>0</v>
@@ -25799,7 +25799,7 @@
         </is>
       </c>
       <c r="L343" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M343" t="n">
         <v>0</v>
@@ -25873,7 +25873,7 @@
         </is>
       </c>
       <c r="L344" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M344" t="n">
         <v>1</v>
@@ -25947,7 +25947,7 @@
         </is>
       </c>
       <c r="L345" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M345" t="n">
         <v>0</v>
@@ -25999,7 +25999,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -26021,7 +26021,7 @@
         </is>
       </c>
       <c r="L346" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M346" t="n">
         <v>0</v>
@@ -26095,7 +26095,7 @@
         </is>
       </c>
       <c r="L347" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M347" t="n">
         <v>0</v>
@@ -26171,7 +26171,7 @@
         </is>
       </c>
       <c r="L348" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M348" t="n">
         <v>0</v>
@@ -26245,7 +26245,7 @@
         </is>
       </c>
       <c r="L349" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M349" t="n">
         <v>0</v>
@@ -26319,7 +26319,7 @@
         </is>
       </c>
       <c r="L350" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M350" t="n">
         <v>0</v>
@@ -26393,7 +26393,7 @@
         </is>
       </c>
       <c r="L351" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M351" t="n">
         <v>0</v>
@@ -26467,7 +26467,7 @@
         </is>
       </c>
       <c r="L352" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M352" t="n">
         <v>0</v>
@@ -26541,7 +26541,7 @@
         </is>
       </c>
       <c r="L353" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M353" t="n">
         <v>0</v>
@@ -26616,7 +26616,7 @@
         </is>
       </c>
       <c r="L354" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M354" t="n">
         <v>0</v>
@@ -26668,7 +26668,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -26690,7 +26690,7 @@
         </is>
       </c>
       <c r="L355" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M355" t="n">
         <v>0</v>
@@ -26764,7 +26764,7 @@
         </is>
       </c>
       <c r="L356" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M356" t="n">
         <v>0</v>
@@ -26838,7 +26838,7 @@
         </is>
       </c>
       <c r="L357" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M357" t="n">
         <v>3</v>
@@ -26912,7 +26912,7 @@
         </is>
       </c>
       <c r="L358" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M358" t="n">
         <v>0</v>
@@ -26986,7 +26986,7 @@
         </is>
       </c>
       <c r="L359" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M359" t="n">
         <v>0</v>
@@ -27060,7 +27060,7 @@
         </is>
       </c>
       <c r="L360" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M360" t="n">
         <v>0</v>
@@ -27134,7 +27134,7 @@
         </is>
       </c>
       <c r="L361" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M361" t="n">
         <v>2</v>
@@ -27208,7 +27208,7 @@
         </is>
       </c>
       <c r="L362" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M362" t="n">
         <v>0</v>
@@ -27282,7 +27282,7 @@
         </is>
       </c>
       <c r="L363" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M363" t="n">
         <v>0</v>
@@ -27356,7 +27356,7 @@
         </is>
       </c>
       <c r="L364" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M364" t="n">
         <v>1</v>
@@ -27430,7 +27430,7 @@
         </is>
       </c>
       <c r="L365" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M365" t="n">
         <v>0</v>
@@ -27504,7 +27504,7 @@
         </is>
       </c>
       <c r="L366" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M366" t="n">
         <v>0</v>
@@ -27578,7 +27578,7 @@
         </is>
       </c>
       <c r="L367" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M367" t="n">
         <v>0</v>
@@ -27652,7 +27652,7 @@
         </is>
       </c>
       <c r="L368" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M368" t="n">
         <v>14</v>
@@ -27726,7 +27726,7 @@
         </is>
       </c>
       <c r="L369" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="M369" t="n">
         <v>0</v>
@@ -27800,7 +27800,7 @@
         </is>
       </c>
       <c r="L370" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M370" t="n">
         <v>0</v>
@@ -27874,7 +27874,7 @@
         </is>
       </c>
       <c r="L371" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M371" t="n">
         <v>0</v>
@@ -27948,7 +27948,7 @@
         </is>
       </c>
       <c r="L372" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M372" t="n">
         <v>1</v>
@@ -28022,7 +28022,7 @@
         </is>
       </c>
       <c r="L373" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="M373" t="n">
         <v>0</v>
@@ -28096,7 +28096,7 @@
         </is>
       </c>
       <c r="L374" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M374" t="n">
         <v>4</v>
@@ -28170,7 +28170,7 @@
         </is>
       </c>
       <c r="L375" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M375" t="n">
         <v>0</v>
@@ -28244,7 +28244,7 @@
         </is>
       </c>
       <c r="L376" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M376" t="n">
         <v>1</v>
@@ -28318,7 +28318,7 @@
         </is>
       </c>
       <c r="L377" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M377" t="n">
         <v>0</v>
@@ -28392,7 +28392,7 @@
         </is>
       </c>
       <c r="L378" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M378" t="n">
         <v>0</v>
@@ -28466,7 +28466,7 @@
         </is>
       </c>
       <c r="L379" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M379" t="n">
         <v>0</v>
@@ -28540,7 +28540,7 @@
         </is>
       </c>
       <c r="L380" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M380" t="n">
         <v>0</v>
@@ -28614,7 +28614,7 @@
         </is>
       </c>
       <c r="L381" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M381" t="n">
         <v>0</v>
@@ -28688,7 +28688,7 @@
         </is>
       </c>
       <c r="L382" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M382" t="n">
         <v>0</v>
@@ -28762,7 +28762,7 @@
         </is>
       </c>
       <c r="L383" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M383" t="n">
         <v>5</v>
@@ -28836,7 +28836,7 @@
         </is>
       </c>
       <c r="L384" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M384" t="n">
         <v>0</v>
@@ -28888,7 +28888,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -28897,7 +28897,7 @@
         </is>
       </c>
       <c r="I385" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J385" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         </is>
       </c>
       <c r="L385" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M385" t="n">
         <v>0</v>
@@ -28984,7 +28984,7 @@
         </is>
       </c>
       <c r="L386" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M386" t="n">
         <v>0</v>
@@ -29058,7 +29058,7 @@
         </is>
       </c>
       <c r="L387" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M387" t="n">
         <v>0</v>
@@ -29132,7 +29132,7 @@
         </is>
       </c>
       <c r="L388" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M388" t="n">
         <v>0</v>
@@ -29206,7 +29206,7 @@
         </is>
       </c>
       <c r="L389" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M389" t="n">
         <v>0</v>
@@ -29280,7 +29280,7 @@
         </is>
       </c>
       <c r="L390" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M390" t="n">
         <v>0</v>
@@ -29354,7 +29354,7 @@
         </is>
       </c>
       <c r="L391" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M391" t="n">
         <v>0</v>
@@ -29428,7 +29428,7 @@
         </is>
       </c>
       <c r="L392" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M392" t="n">
         <v>0</v>
@@ -29502,7 +29502,7 @@
         </is>
       </c>
       <c r="L393" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M393" t="n">
         <v>0</v>
@@ -29576,7 +29576,7 @@
         </is>
       </c>
       <c r="L394" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M394" t="n">
         <v>0</v>
@@ -29650,7 +29650,7 @@
         </is>
       </c>
       <c r="L395" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M395" t="n">
         <v>2</v>
@@ -29702,7 +29702,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -29711,7 +29711,7 @@
         </is>
       </c>
       <c r="I396" t="n">
-        <v>612</v>
+        <v>622</v>
       </c>
       <c r="J396" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         </is>
       </c>
       <c r="L396" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M396" t="n">
         <v>0</v>
@@ -29798,7 +29798,7 @@
         </is>
       </c>
       <c r="L397" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M397" t="n">
         <v>0</v>
@@ -29872,7 +29872,7 @@
         </is>
       </c>
       <c r="L398" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M398" t="n">
         <v>0</v>
@@ -29946,7 +29946,7 @@
         </is>
       </c>
       <c r="L399" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M399" t="n">
         <v>0</v>
@@ -30020,7 +30020,7 @@
         </is>
       </c>
       <c r="L400" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M400" t="n">
         <v>0</v>
@@ -30094,7 +30094,7 @@
         </is>
       </c>
       <c r="L401" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M401" t="n">
         <v>0</v>
@@ -30168,7 +30168,7 @@
         </is>
       </c>
       <c r="L402" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M402" t="n">
         <v>0</v>
@@ -30242,7 +30242,7 @@
         </is>
       </c>
       <c r="L403" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M403" t="n">
         <v>17</v>
@@ -30316,7 +30316,7 @@
         </is>
       </c>
       <c r="L404" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M404" t="n">
         <v>0</v>
@@ -30390,7 +30390,7 @@
         </is>
       </c>
       <c r="L405" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M405" t="n">
         <v>1</v>
@@ -30464,7 +30464,7 @@
         </is>
       </c>
       <c r="L406" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M406" t="n">
         <v>0</v>
@@ -30516,7 +30516,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>2022-10-28</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -30538,7 +30538,7 @@
         </is>
       </c>
       <c r="L407" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M407" t="n">
         <v>0</v>
@@ -30612,7 +30612,7 @@
         </is>
       </c>
       <c r="L408" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M408" t="n">
         <v>0</v>
@@ -30686,7 +30686,7 @@
         </is>
       </c>
       <c r="L409" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M409" t="n">
         <v>0</v>
@@ -30760,7 +30760,7 @@
         </is>
       </c>
       <c r="L410" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M410" t="n">
         <v>0</v>
@@ -30834,7 +30834,7 @@
         </is>
       </c>
       <c r="L411" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M411" t="n">
         <v>3</v>
@@ -30908,7 +30908,7 @@
         </is>
       </c>
       <c r="L412" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M412" t="n">
         <v>0</v>
@@ -30982,7 +30982,7 @@
         </is>
       </c>
       <c r="L413" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M413" t="n">
         <v>0</v>
@@ -31056,7 +31056,7 @@
         </is>
       </c>
       <c r="L414" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M414" t="n">
         <v>0</v>
@@ -31130,7 +31130,7 @@
         </is>
       </c>
       <c r="L415" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M415" t="n">
         <v>0</v>
@@ -31204,7 +31204,7 @@
         </is>
       </c>
       <c r="L416" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M416" t="n">
         <v>0</v>
@@ -31278,7 +31278,7 @@
         </is>
       </c>
       <c r="L417" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M417" t="n">
         <v>0</v>
@@ -31352,7 +31352,7 @@
         </is>
       </c>
       <c r="L418" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M418" t="n">
         <v>0</v>
@@ -31426,7 +31426,7 @@
         </is>
       </c>
       <c r="L419" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M419" t="n">
         <v>0</v>
@@ -31500,7 +31500,7 @@
         </is>
       </c>
       <c r="L420" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M420" t="n">
         <v>0</v>
@@ -31574,7 +31574,7 @@
         </is>
       </c>
       <c r="L421" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M421" t="n">
         <v>0</v>
@@ -31648,7 +31648,7 @@
         </is>
       </c>
       <c r="L422" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M422" t="n">
         <v>0</v>
@@ -31722,7 +31722,7 @@
         </is>
       </c>
       <c r="L423" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M423" t="n">
         <v>0</v>
@@ -31796,7 +31796,7 @@
         </is>
       </c>
       <c r="L424" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M424" t="n">
         <v>0</v>
@@ -31870,7 +31870,7 @@
         </is>
       </c>
       <c r="L425" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M425" t="n">
         <v>0</v>
@@ -31944,7 +31944,7 @@
         </is>
       </c>
       <c r="L426" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M426" t="n">
         <v>0</v>
@@ -32018,7 +32018,7 @@
         </is>
       </c>
       <c r="L427" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M427" t="n">
         <v>0</v>
@@ -32092,7 +32092,7 @@
         </is>
       </c>
       <c r="L428" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M428" t="n">
         <v>5</v>
@@ -32144,7 +32144,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -32153,7 +32153,7 @@
         </is>
       </c>
       <c r="I429" t="n">
-        <v>2973444</v>
+        <v>4022048</v>
       </c>
       <c r="J429" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         </is>
       </c>
       <c r="L429" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M429" t="n">
         <v>0</v>
@@ -32240,7 +32240,7 @@
         </is>
       </c>
       <c r="L430" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M430" t="n">
         <v>0</v>
@@ -32314,7 +32314,7 @@
         </is>
       </c>
       <c r="L431" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M431" t="n">
         <v>0</v>
@@ -32388,7 +32388,7 @@
         </is>
       </c>
       <c r="L432" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M432" t="n">
         <v>0</v>
@@ -32462,7 +32462,7 @@
         </is>
       </c>
       <c r="L433" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M433" t="n">
         <v>0</v>
@@ -32536,7 +32536,7 @@
         </is>
       </c>
       <c r="L434" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M434" t="n">
         <v>0</v>
@@ -32610,7 +32610,7 @@
         </is>
       </c>
       <c r="L435" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M435" t="n">
         <v>0</v>
@@ -32684,7 +32684,7 @@
         </is>
       </c>
       <c r="L436" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M436" t="n">
         <v>1</v>
@@ -32758,7 +32758,7 @@
         </is>
       </c>
       <c r="L437" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M437" t="n">
         <v>0</v>
@@ -32832,7 +32832,7 @@
         </is>
       </c>
       <c r="L438" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M438" t="n">
         <v>0</v>
@@ -32906,7 +32906,7 @@
         </is>
       </c>
       <c r="L439" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M439" t="n">
         <v>0</v>
@@ -32980,7 +32980,7 @@
         </is>
       </c>
       <c r="L440" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M440" t="n">
         <v>0</v>
@@ -33054,7 +33054,7 @@
         </is>
       </c>
       <c r="L441" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M441" t="n">
         <v>0</v>
@@ -33128,7 +33128,7 @@
         </is>
       </c>
       <c r="L442" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M442" t="n">
         <v>0</v>
@@ -33202,7 +33202,7 @@
         </is>
       </c>
       <c r="L443" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M443" t="n">
         <v>3</v>
@@ -33276,7 +33276,7 @@
         </is>
       </c>
       <c r="L444" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M444" t="n">
         <v>0</v>
@@ -33350,7 +33350,7 @@
         </is>
       </c>
       <c r="L445" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M445" t="n">
         <v>0</v>
@@ -33424,7 +33424,7 @@
         </is>
       </c>
       <c r="L446" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="M446" t="n">
         <v>11</v>
@@ -33498,7 +33498,7 @@
         </is>
       </c>
       <c r="L447" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M447" t="n">
         <v>0</v>
@@ -33572,7 +33572,7 @@
         </is>
       </c>
       <c r="L448" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M448" t="n">
         <v>0</v>
@@ -33646,7 +33646,7 @@
         </is>
       </c>
       <c r="L449" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M449" t="n">
         <v>0</v>
@@ -33720,7 +33720,7 @@
         </is>
       </c>
       <c r="L450" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M450" t="n">
         <v>2</v>
@@ -33794,7 +33794,7 @@
         </is>
       </c>
       <c r="L451" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M451" t="n">
         <v>0</v>
@@ -33868,7 +33868,7 @@
         </is>
       </c>
       <c r="L452" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M452" t="n">
         <v>0</v>
@@ -33942,7 +33942,7 @@
         </is>
       </c>
       <c r="L453" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M453" t="n">
         <v>0</v>
@@ -34016,7 +34016,7 @@
         </is>
       </c>
       <c r="L454" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M454" t="n">
         <v>0</v>
@@ -34090,7 +34090,7 @@
         </is>
       </c>
       <c r="L455" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M455" t="n">
         <v>0</v>
@@ -34164,7 +34164,7 @@
         </is>
       </c>
       <c r="L456" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M456" t="n">
         <v>1</v>
@@ -34238,7 +34238,7 @@
         </is>
       </c>
       <c r="L457" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M457" t="n">
         <v>0</v>
@@ -34312,7 +34312,7 @@
         </is>
       </c>
       <c r="L458" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="M458" t="n">
         <v>0</v>
@@ -34386,7 +34386,7 @@
         </is>
       </c>
       <c r="L459" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M459" t="n">
         <v>0</v>
@@ -34460,7 +34460,7 @@
         </is>
       </c>
       <c r="L460" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M460" t="n">
         <v>0</v>
@@ -34534,7 +34534,7 @@
         </is>
       </c>
       <c r="L461" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M461" t="n">
         <v>1</v>
@@ -34608,7 +34608,7 @@
         </is>
       </c>
       <c r="L462" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M462" t="n">
         <v>0</v>
@@ -34682,7 +34682,7 @@
         </is>
       </c>
       <c r="L463" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M463" t="n">
         <v>2</v>
@@ -34756,7 +34756,7 @@
         </is>
       </c>
       <c r="L464" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M464" t="n">
         <v>0</v>
@@ -34830,7 +34830,7 @@
         </is>
       </c>
       <c r="L465" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M465" t="n">
         <v>0</v>
@@ -34904,7 +34904,7 @@
         </is>
       </c>
       <c r="L466" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M466" t="n">
         <v>0</v>
@@ -34978,7 +34978,7 @@
         </is>
       </c>
       <c r="L467" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M467" t="n">
         <v>0</v>
@@ -35052,7 +35052,7 @@
         </is>
       </c>
       <c r="L468" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M468" t="n">
         <v>0</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="L469" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M469" t="n">
         <v>0</v>
@@ -35200,7 +35200,7 @@
         </is>
       </c>
       <c r="L470" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M470" t="n">
         <v>1</v>
@@ -35274,7 +35274,7 @@
         </is>
       </c>
       <c r="L471" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M471" t="n">
         <v>0</v>
@@ -35348,7 +35348,7 @@
         </is>
       </c>
       <c r="L472" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M472" t="n">
         <v>0</v>
@@ -35422,7 +35422,7 @@
         </is>
       </c>
       <c r="L473" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M473" t="n">
         <v>0</v>
@@ -35496,7 +35496,7 @@
         </is>
       </c>
       <c r="L474" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M474" t="n">
         <v>0</v>
@@ -35570,7 +35570,7 @@
         </is>
       </c>
       <c r="L475" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M475" t="n">
         <v>0</v>
@@ -35644,7 +35644,7 @@
         </is>
       </c>
       <c r="L476" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="M476" t="n">
         <v>0</v>
@@ -35718,7 +35718,7 @@
         </is>
       </c>
       <c r="L477" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="M477" t="n">
         <v>0</v>
@@ -35792,7 +35792,7 @@
         </is>
       </c>
       <c r="L478" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M478" t="n">
         <v>0</v>
@@ -35866,7 +35866,7 @@
         </is>
       </c>
       <c r="L479" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M479" t="n">
         <v>0</v>
@@ -35940,7 +35940,7 @@
         </is>
       </c>
       <c r="L480" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M480" t="n">
         <v>0</v>
@@ -36014,7 +36014,7 @@
         </is>
       </c>
       <c r="L481" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M481" t="n">
         <v>10</v>
@@ -36088,7 +36088,7 @@
         </is>
       </c>
       <c r="L482" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M482" t="n">
         <v>0</v>
@@ -36162,7 +36162,7 @@
         </is>
       </c>
       <c r="L483" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M483" t="n">
         <v>0</v>
@@ -36236,7 +36236,7 @@
         </is>
       </c>
       <c r="L484" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M484" t="n">
         <v>0</v>
@@ -36310,7 +36310,7 @@
         </is>
       </c>
       <c r="L485" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M485" t="n">
         <v>0</v>
@@ -36384,7 +36384,7 @@
         </is>
       </c>
       <c r="L486" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M486" t="n">
         <v>1</v>
@@ -36458,7 +36458,7 @@
         </is>
       </c>
       <c r="L487" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M487" t="n">
         <v>0</v>
@@ -36532,7 +36532,7 @@
         </is>
       </c>
       <c r="L488" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M488" t="n">
         <v>3</v>
@@ -36606,7 +36606,7 @@
         </is>
       </c>
       <c r="L489" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M489" t="n">
         <v>0</v>
@@ -36680,7 +36680,7 @@
         </is>
       </c>
       <c r="L490" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M490" t="n">
         <v>0</v>
@@ -36754,7 +36754,7 @@
         </is>
       </c>
       <c r="L491" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M491" t="n">
         <v>0</v>
